--- a/data/trans_bre/CAGE_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/CAGE_R-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE)</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,77; -0,15</t>
+          <t>-1,62; -0,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,1; -0,36</t>
+          <t>-2,15; -0,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,06</t>
+          <t>-1,75; 0,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1,66</t>
+          <t>-1,22; 1,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 17,0</t>
+          <t>-100,0; 7,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 88,0</t>
+          <t>-100,0; 107,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,36; -0,19</t>
+          <t>-1,31; -0,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,41; -0,53</t>
+          <t>-2,44; -0,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,06; -0,97</t>
+          <t>-3,09; -1,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,83</t>
+          <t>-1,46; 3,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 78,69</t>
+          <t>-100,0; inf</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -51,51</t>
+          <t>-100,0; -33,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-96,66; -52,74</t>
+          <t>-96,49; -56,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-55,21; 335,32</t>
+          <t>-59,28; 309,45</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,92; -0,42</t>
+          <t>-2,0; -0,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,75; -1,23</t>
+          <t>-3,67; -1,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; -0,42</t>
+          <t>-1,92; -0,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 2,08</t>
+          <t>-2,96; 1,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -61,95</t>
+          <t>-100,0; -64,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 241,45</t>
+          <t>-100,0; 191,32</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,88</t>
+          <t>-0,75; 0,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,65; -1,46</t>
+          <t>-3,78; -1,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,85</t>
+          <t>-1,14; 0,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,46; -0,85</t>
+          <t>-5,2; -1,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-73,26; 277,61</t>
+          <t>-67,25; 251,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -64,71</t>
+          <t>-100,0; -70,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-61,58; 114,12</t>
+          <t>-63,39; 119,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-90,74; -21,07</t>
+          <t>-92,7; -28,15</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; -0,18</t>
+          <t>-0,86; -0,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,32; -1,31</t>
+          <t>-2,29; -1,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; -0,5</t>
+          <t>-1,47; -0,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 0,27</t>
+          <t>-2,08; 0,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-86,85; -26,54</t>
+          <t>-86,05; -20,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-97,25; -81,54</t>
+          <t>-97,73; -82,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-81,91; -38,73</t>
+          <t>-82,48; -38,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-75,12; 14,99</t>
+          <t>-76,01; 12,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/CAGE_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/CAGE_R-Habitat-trans_bre.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-15,53%</t>
+          <t>-16,22%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,62; -0,25</t>
+          <t>-1,75; -0,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,15; -0,43</t>
+          <t>-2,18; -0,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,07</t>
+          <t>-1,71; 0,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,82</t>
+          <t>-1,17; 1,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 7,12</t>
+          <t>-100,0; -16,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 107,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,7</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,31; -0,19</t>
+          <t>-1,33; -0,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,44; -0,54</t>
+          <t>-2,44; -0,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,09; -1,04</t>
+          <t>-3,18; -1,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 3,69</t>
+          <t>-1,17; 3,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; inf</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -33,27</t>
+          <t>-100,0; -49,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-96,49; -56,43</t>
+          <t>-96,51; -53,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,28; 309,45</t>
+          <t>-54,15; 275,87</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,68</t>
+          <t>-0,47</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-40,45%</t>
+          <t>-17,33%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; -0,44</t>
+          <t>-1,89; -0,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,67; -1,27</t>
+          <t>-3,72; -1,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,92; -0,41</t>
+          <t>-2,01; -0,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 1,89</t>
+          <t>-3,08; 3,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -64,55</t>
+          <t>-100,0; -73,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 191,32</t>
+          <t>-86,04; 325,53</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,85</t>
+          <t>-2,36</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-73,29%</t>
+          <t>-57,85%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,87</t>
+          <t>-0,85; 0,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,78; -1,45</t>
+          <t>-3,73; -1,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,88</t>
+          <t>-1,07; 0,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,2; -1,04</t>
+          <t>-4,42; 0,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-67,25; 251,16</t>
+          <t>-75,61; 211,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -70,59</t>
+          <t>-100,0; -69,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-63,39; 119,11</t>
+          <t>-63,09; 124,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-92,7; -28,15</t>
+          <t>-85,37; 41,64</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,93</t>
+          <t>-0,61</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-41,49%</t>
+          <t>-24,59%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; -0,18</t>
+          <t>-0,88; -0,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,29; -1,28</t>
+          <t>-2,36; -1,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; -0,48</t>
+          <t>-1,46; -0,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,22</t>
+          <t>-1,75; 0,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-86,05; -20,23</t>
+          <t>-84,41; -11,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-97,73; -82,0</t>
+          <t>-97,5; -80,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-82,48; -38,48</t>
+          <t>-82,98; -41,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-76,01; 12,45</t>
+          <t>-61,41; 41,76</t>
         </is>
       </c>
     </row>
